--- a/information_request_forms/001_documentary_footage_license_request_form--information_request_forms.xlsx
+++ b/information_request_forms/001_documentary_footage_license_request_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>usage_purpose</t>
+          <t>What is your intended usage of the documentary footage?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>Which distribution channel(s) do you plan to use for the documentary footage?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>license_duration</t>
+          <t>How long do you plan to license the footage for?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>production_company</t>
+          <t>Which production company produced the documentary?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>archive_name</t>
+          <t>What is the name of the archive that owns the documentary footage?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>media_contact</t>
+          <t>Who is your contact person for this request?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>What is your contact email address?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>What is your contact phone number?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>Can you provide a brief description of the project?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>license_accepted</t>
+          <t>Have you accepted the license terms?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Please sign your name below</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date_signed</t>
+          <t>What date did you sign this form?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>user_name</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>What is your job title?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Which department do you belong to?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>Which company do you represent?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>What is your work address?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>What is your work phone number?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>postal_code</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>postal_code</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fax</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>fax</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>job_title_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>department_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>company_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>address_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>non-commercial_use</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Non-commercial use</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>commercial_use</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Commercial use</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1004,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>personal_project</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Personal project</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>distribution_choices</t>
+          <t>usage_purpose_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>distribution_choices</t>
+          <t>usage_purpose_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,114 +1055,165 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>license_duration_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>vimeo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Vimeo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>license_duration_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>tv_broadcast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>TV broadcast</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>license_duration_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>online_streaming_platform</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Online streaming platform</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>license_accepted_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>license_accepted_choices</t>
+          <t>license_duration_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>one-time_use</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>One-time use</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>license_duration_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ongoing_use</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ongoing use</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>license_duration_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>unknown_or_open-ended</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unknown or open-ended</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>license_accepted_choices</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option3</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>license_accepted_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
